--- a/exports/colleges/25621_national-law-school-of-india-university-nlsiu-bangalore.xlsx
+++ b/exports/colleges/25621_national-law-school-of-india-university-nlsiu-bangalore.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #4</t>
+          <t>Not Ranked</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1179,13 +1179,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1196,17 +1194,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -1218,15 +1206,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
